--- a/output/pdf_financials_xlsx/URC.xlsx
+++ b/output/pdf_financials_xlsx/URC.xlsx
@@ -3014,25 +3014,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.024255</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>7.076311</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.352</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.488</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.319</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.316</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.359</v>
       </c>
     </row>
     <row r="93">
@@ -5266,7 +5266,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -5744,7 +5748,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -6287,7 +6295,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -6936,7 +6948,11 @@
           <t>Warrant Reserves 11</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>2.024255</v>
       </c>

--- a/output/pdf_financials_xlsx/URC.xlsx
+++ b/output/pdf_financials_xlsx/URC.xlsx
@@ -736,22 +736,22 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.158085</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="13">
@@ -1184,22 +1184,22 @@
         <v>-3.819567</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.701358</v>
+        <v>-2.859443</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.377</v>
+        <v>-1.433</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.257</v>
+        <v>-4.294</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.858</v>
+        <v>-5.925</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>7.757</v>
+        <v>7.065</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.308</v>
+        <v>-5.883</v>
       </c>
     </row>
     <row r="28">
@@ -1240,22 +1240,22 @@
         <v>-3.819567</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.701358</v>
+        <v>-2.859443</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.377</v>
+        <v>-1.433</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.255</v>
+        <v>-4.292</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.834</v>
+        <v>-5.901</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.78</v>
+        <v>7.088</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.253</v>
+        <v>-5.828</v>
       </c>
     </row>
     <row r="30">
@@ -1285,13 +1285,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-206.952820148989</v>
+        <v>-209.3295494856332</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>52.72788885123687</v>
+        <v>48.03795323619112</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-148.5156912637829</v>
+        <v>-164.77240599378</v>
       </c>
     </row>
     <row r="31">
@@ -1378,19 +1378,19 @@
         <v>11.837162</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.214</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.385</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>14.306</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>12.935</v>
       </c>
     </row>
     <row r="35">
@@ -1434,19 +1434,19 @@
         <v>42.293623</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>30.045</v>
+        <v>37.259</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>51.787</v>
+        <v>56.172</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>38.34</v>
+        <v>52.646</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>9.143000000000001</v>
+        <v>30.243</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.147</v>
+        <v>20.082</v>
       </c>
     </row>
     <row r="37">
@@ -1770,19 +1770,19 @@
         <v>0.75225</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>7.883</v>
+        <v>0.669</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.082</v>
+        <v>0.697</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14.416</v>
+        <v>0.11</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>21.21</v>
+        <v>0.11</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>13.045</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="49">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">

--- a/output/pdf_financials_xlsx/URC.xlsx
+++ b/output/pdf_financials_xlsx/URC.xlsx
@@ -593,25 +593,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.148502</v>
+        <v>0.461857</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.284876</v>
+        <v>0.811567</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.395</v>
+        <v>0.772</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.608</v>
+        <v>1.08</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.287</v>
+        <v>4.26</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.589</v>
+        <v>5.655</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>5.188</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="8">
@@ -677,25 +677,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.148502</v>
+        <v>0.461857</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.284876</v>
+        <v>0.811567</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.395</v>
+        <v>0.772</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.608</v>
+        <v>1.08</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3.287</v>
+        <v>4.26</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>4.589</v>
+        <v>5.655</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5.188</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="11">
@@ -720,10 +720,10 @@
         <v>-3.782</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>10.166</v>
+        <v>9.1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.651</v>
+        <v>-2.793</v>
       </c>
     </row>
     <row r="12">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3.819567</v>
+        <v>-3.569209</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.701358</v>
+        <v>-2.573231</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.377</v>
+        <v>-0.899</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-4.257</v>
+        <v>-2.065</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-5.858</v>
@@ -873,25 +873,25 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.250358</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.128127</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.478</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.192</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2.023</v>
+        <v>-2.023</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.346</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="18">
@@ -1181,16 +1181,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.819567</v>
+        <v>-3.569209</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.859443</v>
+        <v>-2.731316</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.433</v>
+        <v>-0.955</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.294</v>
+        <v>-2.102</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-5.925</v>
@@ -1237,16 +1237,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.819567</v>
+        <v>-3.569209</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.859443</v>
+        <v>-2.731316</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.433</v>
+        <v>-0.955</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.292</v>
+        <v>-2.1</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.901</v>
@@ -1301,16 +1301,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-7.01438329893262</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.979226505509999</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-53.17018909899889</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-106.1501210653753</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0.2560600887674974</v>
@@ -3643,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>4.681</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>4.296</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -9416,7 +9416,11 @@
           <t>Net proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -11040,7 +11044,11 @@
           <t>Salaries and directors' fees 13</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -11067,10 +11075,10 @@
         </is>
       </c>
       <c r="J139" s="5" t="n">
-        <v>-1.066</v>
+        <v>1.066</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>-1.142</v>
+        <v>1.142</v>
       </c>
     </row>
     <row r="140">
@@ -11628,7 +11636,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12242,7 +12254,11 @@
           <t>Salaries and directors' fees 14</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -12264,10 +12280,10 @@
         </is>
       </c>
       <c r="I163" s="5" t="n">
-        <v>-0.973</v>
+        <v>0.973</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>-1.066</v>
+        <v>1.066</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12391,7 +12407,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -12965,7 +12985,11 @@
           <t>Management and directors' fees 14</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -12980,10 +13004,10 @@
         <v>0.377</v>
       </c>
       <c r="H178" s="5" t="n">
-        <v>-0.472</v>
+        <v>0.472</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>-0.578</v>
+        <v>0.578</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -13876,7 +13900,11 @@
           <t>Management and directors' fees 13</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -14078,7 +14106,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E201" s="5" t="n">
         <v>0.250358</v>
       </c>
@@ -14172,7 +14204,11 @@
           <t>Management and directors' fees 15</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
         <v>0.313355</v>
       </c>
